--- a/data/sim_data.xlsx
+++ b/data/sim_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henaolab/Documents/R/bactcountr_shiny/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD47F09-4742-974C-B499-8DCE68B19DEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00185AEC-389F-CB4A-82A8-60F7C908F783}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30400" yWindow="2840" windowWidth="19840" windowHeight="22380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>group</t>
   </si>
   <si>
-    <t>mouse</t>
-  </si>
-  <si>
     <t>dilution_0</t>
   </si>
   <si>
@@ -90,6 +87,9 @@
   </si>
   <si>
     <t>TNTC</t>
+  </si>
+  <si>
+    <t>replicate</t>
   </si>
 </sst>
 </file>
@@ -525,19 +525,19 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2">
         <v>48</v>
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2">
         <v>58</v>
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D4" s="2">
         <v>81</v>
@@ -605,10 +605,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -625,13 +625,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2">
         <v>14</v>
@@ -645,13 +645,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2">
         <v>10</v>
